--- a/AAII_Financials/Yearly/PMI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PMI_YR_FIN.xlsx
@@ -2072,10 +2072,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7800</v>
+        <v>8300</v>
       </c>
       <c r="E59" s="3">
-        <v>6800</v>
+        <v>7300</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
